--- a/excel_config/indir/委托.xlsx
+++ b/excel_config/indir/委托.xlsx
@@ -1040,17 +1040,17 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
     </row>
@@ -1100,17 +1100,17 @@
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>{"portrait":"res://assets/art/characters/001_cutout_483x512.png","badge":"可接受"}</t>
+          <t>{"portrait": "res://assets/art/characters/001_cutout_483x512.png", "badge": "可接受"}</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>[{"kind":"item","id":"items_LingCao","label":"清心草","count":3,"consume":true},{"kind":"item","id":"items_LingGuo","label":"灵芝","count":2,"consume":true}]</t>
+          <t>[{"kind": "item", "id": "items_LingCao", "label": "清心草", "count": 3, "consume": true}, {"kind": "item", "id": "items_LingGuo", "label": "灵芝", "count": 2, "consume": true}]</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>[{"kind":"item","id":"items_LingCao","count":10},{"kind":"item","id":"items_XuanJin","count":20},{"kind":"currency","id":"ling_stones","count":500}]</t>
+          <t>[{"kind": "item", "id": "items_LingCao", "count": 10}, {"kind": "item", "id": "items_XuanJin", "count": 20}, {"kind": "currency", "id": "ling_stones", "count": 500}]</t>
         </is>
       </c>
     </row>
@@ -1145,17 +1145,17 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>{"portrait":"res://assets/art/characters/004_cutout_502x512.png","badge":"进行中"}</t>
+          <t>{"portrait": "res://assets/art/characters/004_cutout_502x512.png", "badge": "进行中"}</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>[{"kind":"lilian","location_id":"qinglan_mountain","min_steps":3,"require_not_defeated":false}]</t>
+          <t>[{"kind": "lilian", "location_id": "qinglan_mountain", "min_steps": 3, "require_not_defeated": false}]</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>[{"kind":"item","id":"items_LingCao","count":5},{"kind":"item","id":"items_XuanJin","count":10},{"kind":"currency","id":"ling_stones","count":300}]</t>
+          <t>[{"kind": "item", "id": "items_LingCao", "count": 5}, {"kind": "item", "id": "items_XuanJin", "count": 10}, {"kind": "currency", "id": "ling_stones", "count": 300}]</t>
         </is>
       </c>
     </row>
@@ -1190,17 +1190,17 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>{"portrait":"res://assets/art/characters/005_cutout_311x512.png","badge":"可接受"}</t>
+          <t>{"portrait": "res://assets/art/characters/005_cutout_311x512.png", "badge": "可接受"}</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>[{"kind":"item","id":"items_LingCao","label":"灵草","count":8,"consume":true}]</t>
+          <t>[{"kind": "item", "id": "items_LingCao", "label": "灵草", "count": 8, "consume": true}]</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>[{"kind":"item","id":"items_LingCao","count":8},{"kind":"item","id":"items_XuanJin","count":15},{"kind":"currency","id":"ling_stones","count":400}]</t>
+          <t>[{"kind": "item", "id": "items_LingCao", "count": 8}, {"kind": "item", "id": "items_XuanJin", "count": 15}, {"kind": "currency", "id": "ling_stones", "count": 400}]</t>
         </is>
       </c>
     </row>
